--- a/data/trans_dic/P36B08_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,42; 54,03</t>
+          <t>45,87; 54,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,54; 56,13</t>
+          <t>46,85; 56,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,51; 66,15</t>
+          <t>56,09; 66,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,18; 94,74</t>
+          <t>86,58; 95,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,56; 57,61</t>
+          <t>48,31; 57,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,36; 68,34</t>
+          <t>58,69; 68,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,28; 67,93</t>
+          <t>57,91; 67,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,12; 94,76</t>
+          <t>87,02; 95,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,05; 54,35</t>
+          <t>48,4; 54,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,07; 60,5</t>
+          <t>54,11; 60,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59,18; 65,84</t>
+          <t>58,86; 65,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,33; 93,69</t>
+          <t>88,5; 94,68</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,17; 65,64</t>
+          <t>58,21; 65,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,59; 70,87</t>
+          <t>63,4; 70,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,66; 72,02</t>
+          <t>65,07; 72,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,33; 97,14</t>
+          <t>91,24; 96,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,11; 72,74</t>
+          <t>65,18; 72,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,31; 78,73</t>
+          <t>71,83; 79,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,96; 76,18</t>
+          <t>68,4; 75,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>93,12; 97,61</t>
+          <t>93,15; 97,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,61; 67,78</t>
+          <t>62,51; 67,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68,0; 73,31</t>
+          <t>68,19; 73,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67,68; 73,1</t>
+          <t>67,67; 72,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,37; 96,83</t>
+          <t>93,19; 96,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,57; 65,43</t>
+          <t>57,55; 65,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,13; 76,65</t>
+          <t>69,76; 76,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,26; 74,38</t>
+          <t>67,39; 74,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91,35; 95,72</t>
+          <t>91,85; 95,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,62; 75,84</t>
+          <t>68,74; 75,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,4; 83,74</t>
+          <t>77,84; 83,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,54; 80,99</t>
+          <t>74,57; 81,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94,03; 97,01</t>
+          <t>94,67; 97,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,9; 69,42</t>
+          <t>64,23; 69,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74,7; 79,58</t>
+          <t>74,84; 79,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,17; 76,67</t>
+          <t>72,01; 76,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93,32; 96,01</t>
+          <t>93,73; 96,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,01; 69,23</t>
+          <t>59,75; 68,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,66; 76,13</t>
+          <t>68,91; 76,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,61; 74,57</t>
+          <t>67,37; 74,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,74; 98,39</t>
+          <t>92,96; 96,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,28; 80,6</t>
+          <t>73,37; 80,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,49; 86,08</t>
+          <t>79,34; 85,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,98; 83,27</t>
+          <t>77,18; 83,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,2; 97,38</t>
+          <t>95,0; 97,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,82; 73,52</t>
+          <t>67,84; 73,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75,05; 80,38</t>
+          <t>75,25; 80,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,35; 78,12</t>
+          <t>73,32; 78,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,92; 97,6</t>
+          <t>94,53; 96,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,57; 74,63</t>
+          <t>65,53; 75,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,79; 81,18</t>
+          <t>72,83; 81,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,44; 81,44</t>
+          <t>73,95; 81,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,61; 95,01</t>
+          <t>91,62; 95,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,93; 78,55</t>
+          <t>70,04; 78,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,51; 85,89</t>
+          <t>78,03; 85,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,62; 86,15</t>
+          <t>78,99; 86,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95,14; 97,53</t>
+          <t>95,13; 97,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69,08; 75,36</t>
+          <t>68,92; 75,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,84; 82,51</t>
+          <t>77,03; 82,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77,35; 82,87</t>
+          <t>77,55; 82,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,38; 95,81</t>
+          <t>93,88; 96,06</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66,97; 77,38</t>
+          <t>67,18; 77,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77,04; 86,08</t>
+          <t>77,13; 85,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,96; 84,83</t>
+          <t>76,22; 84,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93,1; 97,0</t>
+          <t>93,22; 96,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,55; 82,18</t>
+          <t>73,55; 81,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83,35; 90,35</t>
+          <t>83,49; 90,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,75; 88,36</t>
+          <t>80,63; 88,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,2; 99,33</t>
+          <t>94,92; 97,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72,14; 78,82</t>
+          <t>72,16; 78,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82,03; 87,64</t>
+          <t>81,89; 87,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79,98; 85,45</t>
+          <t>79,95; 85,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95,56; 98,53</t>
+          <t>94,49; 96,94</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>68,6; 80,4</t>
+          <t>69,19; 80,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,25; 89,28</t>
+          <t>79,48; 89,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,76; 87,2</t>
+          <t>78,49; 87,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,89; 97,87</t>
+          <t>94,3; 97,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,1; 81,67</t>
+          <t>71,97; 82,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,51; 89,06</t>
+          <t>81,2; 88,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,73; 83,96</t>
+          <t>74,85; 83,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>94,25; 97,11</t>
+          <t>94,42; 97,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,7; 80,02</t>
+          <t>72,86; 80,4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81,78; 87,48</t>
+          <t>81,67; 87,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77,58; 83,96</t>
+          <t>77,27; 83,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,76; 97,06</t>
+          <t>95,11; 97,2</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>61,48; 64,97</t>
+          <t>61,68; 64,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69,51; 72,71</t>
+          <t>69,56; 72,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70,75; 73,79</t>
+          <t>70,84; 73,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93,31; 95,72</t>
+          <t>93,49; 95,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69,3; 72,52</t>
+          <t>69,41; 72,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,13; 80,83</t>
+          <t>78,08; 80,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,06; 78,81</t>
+          <t>75,86; 78,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>95,18; 96,74</t>
+          <t>95,08; 96,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66,1; 68,46</t>
+          <t>65,9; 68,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74,36; 76,5</t>
+          <t>74,4; 76,46</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73,82; 75,98</t>
+          <t>73,76; 75,88</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,43; 95,93</t>
+          <t>94,46; 95,57</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362717</t>
+          <t>375427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>284493</t>
+          <t>332994</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>647210</t>
+          <t>708421</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>224427; 266966</t>
+          <t>226638; 269651</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>211378; 254902</t>
+          <t>212746; 254490</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>235245; 275338</t>
+          <t>233485; 274960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>336691; 378933</t>
+          <t>353074; 390276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>226501; 268689</t>
+          <t>225314; 266298</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>254819; 293385</t>
+          <t>251957; 292691</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>229535; 267507</t>
+          <t>228057; 267316</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>263466; 296785</t>
+          <t>315468; 344617</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>461552; 522033</t>
+          <t>464901; 523123</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>477643; 534521</t>
+          <t>478066; 536021</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>479402; 533383</t>
+          <t>476808; 531658</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>615663; 668159</t>
+          <t>681729; 729354</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401827</t>
+          <t>450457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>488829</t>
+          <t>477269</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>890656</t>
+          <t>927727</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>427865; 482804</t>
+          <t>428137; 481931</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>436912; 486956</t>
+          <t>435622; 485446</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>380488; 423785</t>
+          <t>382937; 426315</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>386837; 411426</t>
+          <t>435121; 461697</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>407268; 454986</t>
+          <t>407688; 452896</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>435178; 480453</t>
+          <t>438371; 483208</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>385963; 426422</t>
+          <t>382872; 424380</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>475481; 498427</t>
+          <t>465845; 485489</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>852097; 922447</t>
+          <t>850741; 922146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>882151; 951104</t>
+          <t>884649; 953214</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>777136; 839273</t>
+          <t>777013; 836826</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>872259; 904559</t>
+          <t>910504; 942088</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503213</t>
+          <t>584275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>519681</t>
+          <t>598500</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1022893</t>
+          <t>1182775</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>367675; 417896</t>
+          <t>367534; 415835</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>477485; 521888</t>
+          <t>474926; 521986</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>449372; 496989</t>
+          <t>450280; 499425</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>489788; 513219</t>
+          <t>569206; 594784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>473304; 523123</t>
+          <t>474112; 522526</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>549468; 594437</t>
+          <t>552554; 595354</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>491536; 534010</t>
+          <t>491717; 536063</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>510103; 526235</t>
+          <t>588955; 605993</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>848840; 922123</t>
+          <t>853174; 924397</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1038882; 1106683</t>
+          <t>1040794; 1105142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>958093; 1017816</t>
+          <t>955948; 1018862</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1006590; 1035558</t>
+          <t>1164004; 1196080</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>852813</t>
+          <t>665011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>686008</t>
+          <t>707887</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1538821</t>
+          <t>1372897</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>311524; 359425</t>
+          <t>310166; 355554</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>420574; 466365</t>
+          <t>422154; 467981</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>432024; 476518</t>
+          <t>430535; 478856</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>832205; 873470</t>
+          <t>651310; 675631</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>377876; 415629</t>
+          <t>378321; 416415</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>486492; 526886</t>
+          <t>485590; 525899</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>497955; 538649</t>
+          <t>499278; 540438</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>677646; 693174</t>
+          <t>698928; 714899</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>701772; 760775</t>
+          <t>701985; 759841</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>919042; 984403</t>
+          <t>921508; 981587</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>943227; 1004487</t>
+          <t>942777; 1006654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1518280; 1561250</t>
+          <t>1357769; 1385822</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>521815</t>
+          <t>569322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>528335</t>
+          <t>587541</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1050150</t>
+          <t>1156863</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>253026; 287982</t>
+          <t>252867; 289744</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>312581; 348603</t>
+          <t>312758; 348212</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>348728; 386747</t>
+          <t>351154; 388656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>506974; 531588</t>
+          <t>556610; 579608</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>282524; 317311</t>
+          <t>282958; 316937</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>350140; 383018</t>
+          <t>347987; 383243</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>387959; 425130</t>
+          <t>389800; 424922</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>521255; 534357</t>
+          <t>579175; 593858</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545608; 595231</t>
+          <t>544365; 598499</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>672697; 722300</t>
+          <t>674305; 723122</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>748965; 802422</t>
+          <t>750928; 803024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1034054; 1061005</t>
+          <t>1141908; 1168532</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>349911</t>
+          <t>386409</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>593929</t>
+          <t>422926</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>943840</t>
+          <t>809335</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>195955; 226392</t>
+          <t>196553; 226204</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>236291; 264032</t>
+          <t>236583; 263460</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253266; 282842</t>
+          <t>254121; 282915</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>342016; 356336</t>
+          <t>378538; 393369</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>252228; 281829</t>
+          <t>252220; 280761</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>295046; 319825</t>
+          <t>295541; 320394</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>303367; 331939</t>
+          <t>302917; 331171</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>584199; 603234</t>
+          <t>415785; 427518</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>458481; 500892</t>
+          <t>458618; 499912</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>541968; 579036</t>
+          <t>541079; 579360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>567115; 605925</t>
+          <t>566934; 607393</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>931371; 960328</t>
+          <t>797650; 818331</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271604</t>
+          <t>298349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>406939</t>
+          <t>444841</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>678542</t>
+          <t>743190</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>143974; 168739</t>
+          <t>145211; 168275</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>197163; 222118</t>
+          <t>197722; 222915</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202404; 224093</t>
+          <t>201724; 223945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>264786; 276017</t>
+          <t>291789; 303053</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>240749; 272690</t>
+          <t>240307; 274683</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>315476; 344702</t>
+          <t>314277; 343230</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>298041; 334852</t>
+          <t>298523; 334446</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>400154; 412312</t>
+          <t>437462; 450259</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>395329; 435125</t>
+          <t>396214; 437212</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>520009; 556197</t>
+          <t>519316; 557037</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>508802; 550619</t>
+          <t>506761; 549927</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>669575; 685805</t>
+          <t>734986; 751145</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3263898</t>
+          <t>3329251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3508214</t>
+          <t>3571959</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6772113</t>
+          <t>6901209</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2013745; 2128375</t>
+          <t>2020508; 2125928</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2376920; 2486475</t>
+          <t>2378762; 2487264</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2389348; 2491913</t>
+          <t>2392468; 2498647</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3225292; 3308458</t>
+          <t>3298351; 3361511</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2341215; 2449848</t>
+          <t>2344836; 2451375</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2772253; 2868338</t>
+          <t>2770591; 2869215</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2683182; 2780348</t>
+          <t>2676208; 2778115</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3481519; 3538720</t>
+          <t>3547249; 3595058</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4397999; 4555090</t>
+          <t>4385114; 4542259</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5181387; 5330806</t>
+          <t>5183933; 5328090</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5097210; 5246277</t>
+          <t>5092834; 5239708</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6717872; 6824431</t>
+          <t>6856932; 6937159</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B08_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
